--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7449C178-80D7-1A43-87FE-072B96DA163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C43F824-193C-A04C-A226-757F4D92DF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7940" yWindow="940" windowWidth="35320" windowHeight="8660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7940" yWindow="940" windowWidth="38640" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fund {id}" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>source:</t>
   </si>
@@ -156,13 +156,16 @@
   </si>
   <si>
     <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>{edit:nonexistent}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +299,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -367,14 +378,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC4D79B"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -531,12 +542,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -612,6 +617,14 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E840A76-1A21-854F-9DD9-64E53453972A}">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -838,51 +851,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="45" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="46"/>
-      <c r="M1" s="45" t="s">
+      <c r="L1" s="44"/>
+      <c r="M1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
     </row>
     <row r="2" spans="1:28" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="47" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="1"/>
@@ -895,28 +906,26 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="49"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="35" t="s">
-        <v>20</v>
-      </c>
+      <c r="O2" s="34"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="52"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="12"/>
@@ -936,9 +945,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="36" t="s">
-        <v>28</v>
-      </c>
+      <c r="O3" s="34"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="12"/>
@@ -949,7 +956,7 @@
       <c r="W3" s="12"/>
       <c r="X3" s="12"/>
       <c r="Y3" s="12"/>
-      <c r="Z3" s="53"/>
+      <c r="Z3" s="51"/>
       <c r="AA3" s="12"/>
       <c r="AB3" s="12"/>
     </row>
@@ -972,9 +979,7 @@
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="10"/>
-      <c r="O4" s="37" t="s">
-        <v>29</v>
-      </c>
+      <c r="O4" s="35"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="12"/>
@@ -985,9 +990,9 @@
       <c r="W4" s="12"/>
       <c r="X4" s="12"/>
       <c r="Y4" s="12"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
     </row>
     <row r="5" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
@@ -1087,31 +1092,31 @@
       <c r="O6" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="57"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="55"/>
+      <c r="Y6" s="55"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="55"/>
     </row>
     <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="58" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="32" t="s">
@@ -1138,10 +1143,10 @@
       <c r="L7" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="61" t="s">
+      <c r="M7" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="61" t="s">
+      <c r="N7" s="59" t="s">
         <v>25</v>
       </c>
       <c r="O7" s="33" t="s">
@@ -1225,6 +1230,31 @@
       <c r="AA9" s="13"/>
       <c r="AB9" s="13"/>
     </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="O11" s="60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="O12" s="61" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="O13" s="34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="O14" s="62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="O15" s="63" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" display="https://uk.wikisource.org/wiki/Архів:ЦДІАК/301" xr:uid="{5E4D837F-1875-864C-BFD9-449B7B93E64E}"/>

--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C43F824-193C-A04C-A226-757F4D92DF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA06C57E-404E-8047-8565-D88D941483F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7940" yWindow="940" windowWidth="38640" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="940" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fund {id}" sheetId="3" r:id="rId1"/>
@@ -155,10 +155,10 @@
     <t>{unquoted_url:linked}</t>
   </si>
   <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
     <t>{edit:nonexistent}</t>
+  </si>
+  <si>
+    <t>{doc_url:doc_link}</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O15" s="63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA06C57E-404E-8047-8565-D88D941483F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC96D4C-4329-EC45-A1DD-8BF4033AA952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="940" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,9 +146,6 @@
     <t>reference date:</t>
   </si>
   <si>
-    <t>YYYY-YYYY</t>
-  </si>
-  <si>
     <t>{parent.name}</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>{doc_url:doc_link}</t>
+  </si>
+  <si>
+    <t>{dates}</t>
   </si>
 </sst>
 </file>
@@ -852,7 +852,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
@@ -926,14 +926,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="5"/>
@@ -965,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O15" s="63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC96D4C-4329-EC45-A1DD-8BF4033AA952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE573F-62EF-CF41-B718-7579EA4BF5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="940" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27120" yWindow="12900" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fund {id}" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>source:</t>
   </si>
@@ -104,12 +104,6 @@
     <t>{description}</t>
   </si>
   <si>
-    <t>=ROWS(__COL__)</t>
-  </si>
-  <si>
-    <t>=SUM(__COL__)</t>
-  </si>
-  <si>
     <t>{empty}</t>
   </si>
   <si>
@@ -146,9 +140,6 @@
     <t>reference date:</t>
   </si>
   <si>
-    <t>{parent.name}</t>
-  </si>
-  <si>
     <t>{unquoted_url:linked}</t>
   </si>
   <si>
@@ -159,6 +150,42 @@
   </si>
   <si>
     <t>{dates}</t>
+  </si>
+  <si>
+    <t>{parent.clean_name}</t>
+  </si>
+  <si>
+    <t>=ROWS($A$__FIRST__:$A__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(E$__FIRST__:E__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(N$__FIRST__:N__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(M$__FIRST__:M__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(L$__FIRST__:L__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(K$__FIRST__:K__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(J$__FIRST__:J__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(I$__FIRST__:I__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(H$__FIRST__:H__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(G$__FIRST__:G__LAST__)</t>
+  </si>
+  <si>
+    <t>=SUM(F$__FIRST__:F__LAST__)</t>
   </si>
 </sst>
 </file>
@@ -843,7 +870,7 @@
   <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="40.1640625" customWidth="1"/>
     <col min="15" max="15" width="40.1640625" customWidth="1"/>
     <col min="16" max="20" width="9.1640625" customWidth="1"/>
@@ -852,11 +879,11 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="40"/>
@@ -868,14 +895,14 @@
       <c r="I1" s="36"/>
       <c r="J1" s="40"/>
       <c r="K1" s="43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L1" s="44"/>
       <c r="M1" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N1" s="45" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O1" s="34"/>
       <c r="P1" s="39"/>
@@ -926,14 +953,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="5"/>
@@ -965,7 +992,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -994,7 +1021,7 @@
       <c r="AA4" s="53"/>
       <c r="AB4" s="53"/>
     </row>
-    <row r="5" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27"/>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
@@ -1002,34 +1029,34 @@
         <v>1</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="28"/>
@@ -1108,49 +1135,49 @@
     </row>
     <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>32</v>
-      </c>
       <c r="D7" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>27</v>
-      </c>
       <c r="I7" s="32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M7" s="59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N7" s="59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -1198,7 +1225,7 @@
     </row>
     <row r="9" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>18</v>
@@ -1242,17 +1269,17 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O13" s="34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O14" s="62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O15" s="63" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE573F-62EF-CF41-B718-7579EA4BF5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3DAD1-153B-4B4D-9EA6-B3C9105991DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27120" yWindow="12900" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -152,9 +152,6 @@
     <t>{dates}</t>
   </si>
   <si>
-    <t>{parent.clean_name}</t>
-  </si>
-  <si>
     <t>=ROWS($A$__FIRST__:$A__LAST__)</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>=SUM(F$__FIRST__:F__LAST__)</t>
+  </si>
+  <si>
+    <t>{archive_name}</t>
   </si>
 </sst>
 </file>
@@ -879,7 +879,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
@@ -1029,34 +1029,34 @@
         <v>1</v>
       </c>
       <c r="E5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>42</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="28"/>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="9" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>18</v>

--- a/resources/xlsx_templates/fond.xlsx
+++ b/resources/xlsx_templates/fond.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3DAD1-153B-4B4D-9EA6-B3C9105991DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E45034-7282-4D4D-AA65-7571976C510B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27120" yWindow="12900" windowWidth="36000" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>{edit:changed}</t>
   </si>
   <si>
-    <t>{id}</t>
-  </si>
-  <si>
     <t>{description}</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>{archive_name}</t>
+  </si>
+  <si>
+    <t>{id:transliterated}</t>
   </si>
 </sst>
 </file>
@@ -879,30 +879,30 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="40"/>
       <c r="F1" s="41"/>
       <c r="G1" s="42" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="H1" s="42"/>
       <c r="I1" s="36"/>
       <c r="J1" s="40"/>
       <c r="K1" s="43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L1" s="44"/>
       <c r="M1" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N1" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O1" s="34"/>
       <c r="P1" s="39"/>
@@ -921,7 +921,7 @@
     </row>
     <row r="2" spans="1:28" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -953,14 +953,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="5"/>
@@ -992,7 +992,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
@@ -1029,34 +1029,34 @@
         <v>1</v>
       </c>
       <c r="E5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>41</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="28"/>
@@ -1135,49 +1135,49 @@
     </row>
     <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="C7" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="57" t="s">
-        <v>30</v>
-      </c>
       <c r="D7" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>24</v>
-      </c>
       <c r="M7" s="59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N7" s="59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="9" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>18</v>
@@ -1269,17 +1269,17 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O13" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O14" s="62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="O15" s="63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
